--- a/inventory/files/2026-W42/STA_AU_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_AU_AUTO_2026-W42.xlsx
@@ -1694,17 +1694,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1361</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-TRKITA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11">
@@ -1714,27 +1714,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>386</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA</t>
+          <t>AH-RCPL-B14A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>362</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-TRKITA</t>
+          <t>AH-RCPAINTA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>355</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
